--- a/resource/excel_download_test.xlsx
+++ b/resource/excel_download_test.xlsx
@@ -16,13 +16,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>内容</t>
+    <t>姓名</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>标题</t>
+    <t>性别</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张三</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -69,8 +81,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -367,15 +382,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>44197</v>
       </c>
     </row>
   </sheetData>
